--- a/Images/Results.xlsx
+++ b/Images/Results.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="238">
   <si>
     <t>Country</t>
   </si>
@@ -191,6 +191,9 @@
     <t>Congo (DR)</t>
   </si>
   <si>
+    <t>Cook Islands</t>
+  </si>
+  <si>
     <t>Costa Rica</t>
   </si>
   <si>
@@ -242,6 +245,9 @@
     <t>Ethiopia</t>
   </si>
   <si>
+    <t>Federated States of Micronesia</t>
+  </si>
+  <si>
     <t>Fiji</t>
   </si>
   <si>
@@ -410,9 +416,6 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
-  </si>
-  <si>
     <t>Moldova</t>
   </si>
   <si>
@@ -456,6 +459,9 @@
   </si>
   <si>
     <t>Nigeria</t>
+  </si>
+  <si>
+    <t>Niue</t>
   </si>
   <si>
     <t>North Macedonia</t>
@@ -773,7 +779,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE1FFE1"/>
+        <fgColor rgb="FFD7FFD7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -785,19 +791,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAFFFAF"/>
+        <fgColor rgb="FFA5FFA5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB9FFB9"/>
+        <fgColor rgb="FFE1FFE1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF87FF87"/>
+        <fgColor rgb="FFC3FFC3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91FF91"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -815,7 +827,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD7FFD7"/>
+        <fgColor rgb="FFB9FFB9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -828,12 +840,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF9BFF9B"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3FFC3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1195,7 +1201,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0000-0000-0000-000000000000}">
-  <dimension ref="A1:F203"/>
+  <dimension ref="A1:F205"/>
   <!-- B4P: Example: A1:Z9 -->
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <!-- $Def Width Height$ -->
@@ -2035,19 +2041,19 @@
         <v>51</v>
       </c>
       <c r="B42" s="5">
-        <v>51100</v>
+        <v>236</v>
       </c>
       <c r="C42" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D42" s="5">
-        <v>5105525</v>
+        <v>14.222</v>
       </c>
       <c r="E42" s="6">
-        <v>0.0366933962</v>
+        <v>0.9987633043</v>
       </c>
       <c r="F42" s="7">
-        <v>103.7181996086</v>
+        <v>48.7288135593</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2055,19 +2061,19 @@
         <v>52</v>
       </c>
       <c r="B43" s="5">
-        <v>56594</v>
+        <v>51100</v>
       </c>
       <c r="C43" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D43" s="5">
-        <v>3896023</v>
+        <v>5105525</v>
       </c>
       <c r="E43" s="6">
-        <v>0.0010197436</v>
+        <v>0.0366933962</v>
       </c>
       <c r="F43" s="7">
-        <v>68.9118987879</v>
+        <v>103.7181996086</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2075,19 +2081,19 @@
         <v>53</v>
       </c>
       <c r="B44" s="5">
-        <v>110860</v>
+        <v>56594</v>
       </c>
       <c r="C44" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D44" s="5">
-        <v>11019931</v>
+        <v>3896023</v>
       </c>
       <c r="E44" s="6">
-        <v>-0.0018119091</v>
+        <v>0.0010197436</v>
       </c>
       <c r="F44" s="7">
-        <v>99.2242467978</v>
+        <v>68.9118987879</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2095,19 +2101,19 @@
         <v>54</v>
       </c>
       <c r="B45" s="5">
-        <v>9251</v>
+        <v>110860</v>
       </c>
       <c r="C45" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D45" s="5">
-        <v>1344976</v>
+        <v>11019931</v>
       </c>
       <c r="E45" s="6">
-        <v>0.0393028571</v>
+        <v>-0.0018119091</v>
       </c>
       <c r="F45" s="7">
-        <v>151.3349908118</v>
+        <v>99.2242467978</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2115,19 +2121,19 @@
         <v>55</v>
       </c>
       <c r="B46" s="5">
-        <v>78867</v>
+        <v>9251</v>
       </c>
       <c r="C46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D46" s="5">
-        <v>10809716</v>
+        <v>1344976</v>
       </c>
       <c r="E46" s="6">
-        <v>0.0172985455</v>
+        <v>0.0393028571</v>
       </c>
       <c r="F46" s="7">
-        <v>139.4753192083</v>
+        <v>151.3349908118</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2135,19 +2141,19 @@
         <v>56</v>
       </c>
       <c r="B47" s="5">
-        <v>42952</v>
+        <v>78867</v>
       </c>
       <c r="C47" t="s">
         <v>9</v>
       </c>
       <c r="D47" s="5">
-        <v>5948136</v>
+        <v>10809716</v>
       </c>
       <c r="E47" s="6">
-        <v>0</v>
+        <v>0.0172985455</v>
       </c>
       <c r="F47" s="7">
-        <v>138.4833302291</v>
+        <v>139.4753192083</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2155,19 +2161,19 @@
         <v>57</v>
       </c>
       <c r="B48" s="5">
-        <v>23200</v>
+        <v>42952</v>
       </c>
       <c r="C48" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D48" s="5">
-        <v>1152944</v>
+        <v>5948136</v>
       </c>
       <c r="E48" s="6">
-        <v>-0.152944</v>
+        <v>0</v>
       </c>
       <c r="F48" s="7">
-        <v>43.1034482759</v>
+        <v>138.4833302291</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2175,19 +2181,19 @@
         <v>58</v>
       </c>
       <c r="B49" s="5">
-        <v>751</v>
+        <v>23200</v>
       </c>
       <c r="C49" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D49" s="5">
-        <v>66.51</v>
+        <v>1152944</v>
       </c>
       <c r="E49" s="6">
-        <v>0.9990498571</v>
+        <v>-0.152944</v>
       </c>
       <c r="F49" s="7">
-        <v>93.2090545939</v>
+        <v>43.1034482759</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2195,19 +2201,19 @@
         <v>59</v>
       </c>
       <c r="B50" s="5">
-        <v>48670</v>
+        <v>751</v>
       </c>
       <c r="C50" t="s">
         <v>15</v>
       </c>
       <c r="D50" s="5">
-        <v>11331265</v>
+        <v>66.51</v>
       </c>
       <c r="E50" s="6">
-        <v>-0.0491912037</v>
+        <v>0.9990498571</v>
       </c>
       <c r="F50" s="7">
-        <v>221.9026094103</v>
+        <v>93.2090545939</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2215,19 +2221,19 @@
         <v>60</v>
       </c>
       <c r="B51" s="5">
-        <v>283561</v>
+        <v>48670</v>
       </c>
       <c r="C51" t="s">
         <v>15</v>
       </c>
       <c r="D51" s="5">
-        <v>17980083</v>
+        <v>11331265</v>
       </c>
       <c r="E51" s="6">
-        <v>0.0174818033</v>
+        <v>-0.0491912037</v>
       </c>
       <c r="F51" s="7">
-        <v>64.5363784159</v>
+        <v>221.9026094103</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2235,19 +2241,19 @@
         <v>61</v>
       </c>
       <c r="B52" s="5">
-        <v>1001450</v>
+        <v>283561</v>
       </c>
       <c r="C52" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D52" s="5">
-        <v>114535772</v>
+        <v>17980083</v>
       </c>
       <c r="E52" s="6">
-        <v>-0.0774766886</v>
+        <v>0.0174818033</v>
       </c>
       <c r="F52" s="7">
-        <v>106.1460881722</v>
+        <v>64.5363784159</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2255,19 +2261,19 @@
         <v>62</v>
       </c>
       <c r="B53" s="5">
-        <v>21041</v>
+        <v>1001450</v>
       </c>
       <c r="C53" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D53" s="5">
-        <v>6309624</v>
+        <v>114535772</v>
       </c>
       <c r="E53" s="6">
-        <v>-0.001527619</v>
+        <v>-0.0774766886</v>
       </c>
       <c r="F53" s="7">
-        <v>299.4154270234</v>
+        <v>106.1460881722</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2275,19 +2281,19 @@
         <v>63</v>
       </c>
       <c r="B54" s="5">
-        <v>28051</v>
+        <v>21041</v>
       </c>
       <c r="C54" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D54" s="5">
-        <v>1847549</v>
+        <v>6309624</v>
       </c>
       <c r="E54" s="6">
-        <v>0.0276057895</v>
+        <v>-0.001527619</v>
       </c>
       <c r="F54" s="7">
-        <v>67.7337706321</v>
+        <v>299.4154270234</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2295,19 +2301,19 @@
         <v>64</v>
       </c>
       <c r="B55" s="5">
-        <v>117600</v>
+        <v>28051</v>
       </c>
       <c r="C55" t="s">
         <v>11</v>
       </c>
       <c r="D55" s="5">
-        <v>3470390</v>
+        <v>1847549</v>
       </c>
       <c r="E55" s="6">
-        <v>0.00846</v>
+        <v>0.0276057895</v>
       </c>
       <c r="F55" s="7">
-        <v>29.7619047619</v>
+        <v>67.7337706321</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2315,19 +2321,19 @@
         <v>65</v>
       </c>
       <c r="B56" s="5">
-        <v>45228</v>
+        <v>117600</v>
       </c>
       <c r="C56" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D56" s="5">
-        <v>1367196</v>
+        <v>3470390</v>
       </c>
       <c r="E56" s="6">
-        <v>0.0234314286</v>
+        <v>0.00846</v>
       </c>
       <c r="F56" s="7">
-        <v>30.9542761121</v>
+        <v>29.7619047619</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2335,19 +2341,19 @@
         <v>66</v>
       </c>
       <c r="B57" s="5">
-        <v>17364</v>
+        <v>45228</v>
       </c>
       <c r="C57" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D57" s="5">
-        <v>1230506</v>
+        <v>1367196</v>
       </c>
       <c r="E57" s="6">
-        <v>-0.0254216667</v>
+        <v>0.0234314286</v>
       </c>
       <c r="F57" s="7">
-        <v>69.1085003455</v>
+        <v>30.9542761121</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2355,19 +2361,19 @@
         <v>67</v>
       </c>
       <c r="B58" s="5">
-        <v>1104300</v>
+        <v>17364</v>
       </c>
       <c r="C58" t="s">
         <v>11</v>
       </c>
       <c r="D58" s="5">
-        <v>128691692</v>
+        <v>1230506</v>
       </c>
       <c r="E58" s="6">
-        <v>0.0077741557</v>
+        <v>-0.0254216667</v>
       </c>
       <c r="F58" s="7">
-        <v>117.4499683057</v>
+        <v>69.1085003455</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2375,59 +2381,53 @@
         <v>68</v>
       </c>
       <c r="B59" s="5">
-        <v>18274</v>
+        <v>1104300</v>
       </c>
       <c r="C59" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D59" s="5">
-        <v>924.145</v>
+        <v>128691692</v>
       </c>
       <c r="E59" s="6">
-        <v>0.9989731722</v>
+        <v>0.0077741557</v>
       </c>
       <c r="F59" s="7">
-        <v>49.2503009741</v>
+        <v>117.4499683057</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>69</v>
       </c>
-      <c r="B60" s="5">
-        <v>338145</v>
-      </c>
+      <c r="B60" s="5"/>
       <c r="C60" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D60" s="5">
-        <v>5601185</v>
-      </c>
-      <c r="E60" s="6">
-        <v>-0.0002116071</v>
-      </c>
-      <c r="F60" s="7">
-        <v>16.5609427908</v>
-      </c>
+        <v>112.63</v>
+      </c>
+      <c r="E60" s="6"/>
+      <c r="F60" s="7"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>70</v>
       </c>
       <c r="B61" s="5">
-        <v>551500</v>
+        <v>18274</v>
       </c>
       <c r="C61" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D61" s="5">
-        <v>66438822</v>
+        <v>924.145</v>
       </c>
       <c r="E61" s="6">
-        <v>-0.0020938462</v>
+        <v>0.9989731722</v>
       </c>
       <c r="F61" s="7">
-        <v>120.2175883953</v>
+        <v>49.2503009741</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2435,19 +2435,19 @@
         <v>71</v>
       </c>
       <c r="B62" s="5">
-        <v>267667</v>
+        <v>338145</v>
       </c>
       <c r="C62" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D62" s="5">
-        <v>2484789</v>
+        <v>5601185</v>
       </c>
       <c r="E62" s="6">
-        <v>0.0060844</v>
+        <v>-0.0002116071</v>
       </c>
       <c r="F62" s="7">
-        <v>9.3399634621</v>
+        <v>16.5609427908</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2455,19 +2455,19 @@
         <v>72</v>
       </c>
       <c r="B63" s="5">
-        <v>11295</v>
+        <v>551500</v>
       </c>
       <c r="C63" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D63" s="5">
-        <v>2697845</v>
+        <v>66438822</v>
       </c>
       <c r="E63" s="6">
-        <v>0.0364839286</v>
+        <v>-0.0020938462</v>
       </c>
       <c r="F63" s="7">
-        <v>247.8972996901</v>
+        <v>120.2175883953</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2475,19 +2475,19 @@
         <v>73</v>
       </c>
       <c r="B64" s="5">
-        <v>69700</v>
+        <v>267667</v>
       </c>
       <c r="C64" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D64" s="5">
-        <v>3807492</v>
+        <v>2484789</v>
       </c>
       <c r="E64" s="6">
-        <v>-0.0290518919</v>
+        <v>0.0060844</v>
       </c>
       <c r="F64" s="7">
-        <v>53.0846484935</v>
+        <v>9.3399634621</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2495,19 +2495,19 @@
         <v>74</v>
       </c>
       <c r="B65" s="5">
-        <v>357022</v>
+        <v>11295</v>
       </c>
       <c r="C65" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D65" s="5">
-        <v>84548231</v>
+        <v>2697845</v>
       </c>
       <c r="E65" s="6">
-        <v>0.0041433333</v>
+        <v>0.0364839286</v>
       </c>
       <c r="F65" s="7">
-        <v>237.8004716796</v>
+        <v>247.8972996901</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2515,19 +2515,19 @@
         <v>75</v>
       </c>
       <c r="B66" s="5">
-        <v>238533</v>
+        <v>69700</v>
       </c>
       <c r="C66" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D66" s="5">
-        <v>33787914</v>
+        <v>3807492</v>
       </c>
       <c r="E66" s="6">
-        <v>-0.0332695413</v>
+        <v>-0.0290518919</v>
       </c>
       <c r="F66" s="7">
-        <v>137.087950095</v>
+        <v>53.0846484935</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2535,19 +2535,19 @@
         <v>76</v>
       </c>
       <c r="B67" s="5">
-        <v>131957</v>
+        <v>357022</v>
       </c>
       <c r="C67" t="s">
         <v>9</v>
       </c>
       <c r="D67" s="5">
-        <v>10242908</v>
+        <v>84548231</v>
       </c>
       <c r="E67" s="6">
-        <v>-0.0346371717</v>
+        <v>0.0041433333</v>
       </c>
       <c r="F67" s="7">
-        <v>75.0244397796</v>
+        <v>237.8004716796</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2555,19 +2555,19 @@
         <v>77</v>
       </c>
       <c r="B68" s="5">
-        <v>344</v>
+        <v>238533</v>
       </c>
       <c r="C68" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D68" s="5">
-        <v>117.081</v>
+        <v>33787914</v>
       </c>
       <c r="E68" s="6">
-        <v>0.99882919</v>
+        <v>-0.0332695413</v>
       </c>
       <c r="F68" s="7">
-        <v>290.6976744186</v>
+        <v>137.087950095</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2575,19 +2575,19 @@
         <v>78</v>
       </c>
       <c r="B69" s="5">
-        <v>108889</v>
+        <v>131957</v>
       </c>
       <c r="C69" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D69" s="5">
-        <v>18124838</v>
+        <v>10242908</v>
       </c>
       <c r="E69" s="6">
-        <v>-0.0182493258</v>
+        <v>-0.0346371717</v>
       </c>
       <c r="F69" s="7">
-        <v>163.4692209498</v>
+        <v>75.0244397796</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2595,19 +2595,19 @@
         <v>79</v>
       </c>
       <c r="B70" s="5">
-        <v>245857</v>
+        <v>344</v>
       </c>
       <c r="C70" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D70" s="5">
-        <v>14405465</v>
+        <v>117.081</v>
       </c>
       <c r="E70" s="6">
-        <v>-0.0289617857</v>
+        <v>0.99882919</v>
       </c>
       <c r="F70" s="7">
-        <v>56.9436705077</v>
+        <v>290.6976744186</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2615,19 +2615,19 @@
         <v>80</v>
       </c>
       <c r="B71" s="5">
-        <v>36125</v>
+        <v>108889</v>
       </c>
       <c r="C71" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D71" s="5">
-        <v>2153339</v>
+        <v>18124838</v>
       </c>
       <c r="E71" s="6">
-        <v>0.0212095455</v>
+        <v>-0.0182493258</v>
       </c>
       <c r="F71" s="7">
-        <v>60.8996539792</v>
+        <v>163.4692209498</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2635,19 +2635,19 @@
         <v>81</v>
       </c>
       <c r="B72" s="5">
-        <v>214969</v>
+        <v>245857</v>
       </c>
       <c r="C72" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D72" s="5">
-        <v>826.353</v>
+        <v>14405465</v>
       </c>
       <c r="E72" s="6">
-        <v>0.9989670588</v>
+        <v>-0.0289617857</v>
       </c>
       <c r="F72" s="7">
-        <v>3.7214668161</v>
+        <v>56.9436705077</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2655,19 +2655,19 @@
         <v>82</v>
       </c>
       <c r="B73" s="5">
-        <v>27750</v>
+        <v>36125</v>
       </c>
       <c r="C73" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D73" s="5">
-        <v>11637398</v>
+        <v>2153339</v>
       </c>
       <c r="E73" s="6">
-        <v>0.0137798305</v>
+        <v>0.0212095455</v>
       </c>
       <c r="F73" s="7">
-        <v>425.2252252252</v>
+        <v>60.8996539792</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2675,19 +2675,19 @@
         <v>83</v>
       </c>
       <c r="B74" s="5">
-        <v>112090</v>
+        <v>214969</v>
       </c>
       <c r="C74" t="s">
         <v>15</v>
       </c>
       <c r="D74" s="5">
-        <v>10644851</v>
+        <v>826.353</v>
       </c>
       <c r="E74" s="6">
-        <v>-0.0752374747</v>
+        <v>0.9989670588</v>
       </c>
       <c r="F74" s="7">
-        <v>88.3218842002</v>
+        <v>3.7214668161</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2695,19 +2695,19 @@
         <v>84</v>
       </c>
       <c r="B75" s="5">
-        <v>93028</v>
+        <v>27750</v>
       </c>
       <c r="C75" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D75" s="5">
-        <v>9686463</v>
+        <v>11637398</v>
       </c>
       <c r="E75" s="6">
-        <v>-0.0090065625</v>
+        <v>0.0137798305</v>
       </c>
       <c r="F75" s="7">
-        <v>103.1947370684</v>
+        <v>425.2252252252</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2715,19 +2715,19 @@
         <v>85</v>
       </c>
       <c r="B76" s="5">
-        <v>103000</v>
+        <v>112090</v>
       </c>
       <c r="C76" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D76" s="5">
-        <v>387.558</v>
+        <v>10644851</v>
       </c>
       <c r="E76" s="6">
-        <v>0.999031105</v>
+        <v>-0.0752374747</v>
       </c>
       <c r="F76" s="7">
-        <v>3.8834951456</v>
+        <v>88.3218842002</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2735,19 +2735,19 @@
         <v>86</v>
       </c>
       <c r="B77" s="5">
-        <v>3287263</v>
+        <v>93028</v>
       </c>
       <c r="C77" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D77" s="5">
-        <v>1438069596</v>
+        <v>9686463</v>
       </c>
       <c r="E77" s="6">
-        <v>0.0025181411</v>
+        <v>-0.0090065625</v>
       </c>
       <c r="F77" s="7">
-        <v>438.5715411271</v>
+        <v>103.1947370684</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -2755,19 +2755,19 @@
         <v>87</v>
       </c>
       <c r="B78" s="5">
-        <v>1904569</v>
+        <v>103000</v>
       </c>
       <c r="C78" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D78" s="5">
-        <v>281190067</v>
+        <v>387.558</v>
       </c>
       <c r="E78" s="6">
-        <v>0.001455728</v>
+        <v>0.999031105</v>
       </c>
       <c r="F78" s="7">
-        <v>147.8549740125</v>
+        <v>3.8834951456</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2775,19 +2775,19 @@
         <v>88</v>
       </c>
       <c r="B79" s="5">
-        <v>1648195</v>
+        <v>3287263</v>
       </c>
       <c r="C79" t="s">
         <v>7</v>
       </c>
       <c r="D79" s="5">
-        <v>90608707</v>
+        <v>1438069596</v>
       </c>
       <c r="E79" s="6">
-        <v>0.010821976</v>
+        <v>0.0025181411</v>
       </c>
       <c r="F79" s="7">
-        <v>55.5759482343</v>
+        <v>438.5715411271</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -2795,19 +2795,19 @@
         <v>89</v>
       </c>
       <c r="B80" s="5">
-        <v>438317</v>
+        <v>1904569</v>
       </c>
       <c r="C80" t="s">
         <v>7</v>
       </c>
       <c r="D80" s="5">
-        <v>45074049</v>
+        <v>281190067</v>
       </c>
       <c r="E80" s="6">
-        <v>-0.0151812838</v>
+        <v>0.001455728</v>
       </c>
       <c r="F80" s="7">
-        <v>101.2965502137</v>
+        <v>147.8549740125</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -2815,19 +2815,19 @@
         <v>90</v>
       </c>
       <c r="B81" s="5">
-        <v>70273</v>
+        <v>1648195</v>
       </c>
       <c r="C81" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D81" s="5">
-        <v>5196630</v>
+        <v>90608707</v>
       </c>
       <c r="E81" s="6">
-        <v>0.0551581818</v>
+        <v>0.010821976</v>
       </c>
       <c r="F81" s="7">
-        <v>78.2661904288</v>
+        <v>55.5759482343</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -2835,19 +2835,19 @@
         <v>91</v>
       </c>
       <c r="B82" s="5">
-        <v>22380</v>
+        <v>438317</v>
       </c>
       <c r="C82" t="s">
         <v>7</v>
       </c>
       <c r="D82" s="5">
-        <v>9256314</v>
+        <v>45074049</v>
       </c>
       <c r="E82" s="6">
-        <v>0.0650187879</v>
+        <v>-0.0151812838</v>
       </c>
       <c r="F82" s="7">
-        <v>442.3592493298</v>
+        <v>101.2965502137</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -2855,19 +2855,19 @@
         <v>92</v>
       </c>
       <c r="B83" s="5">
-        <v>301340</v>
+        <v>70273</v>
       </c>
       <c r="C83" t="s">
         <v>9</v>
       </c>
       <c r="D83" s="5">
-        <v>59499453</v>
+        <v>5196630</v>
       </c>
       <c r="E83" s="6">
-        <v>-0.0084653051</v>
+        <v>0.0551581818</v>
       </c>
       <c r="F83" s="7">
-        <v>195.7921284927</v>
+        <v>78.2661904288</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -2875,19 +2875,19 @@
         <v>93</v>
       </c>
       <c r="B84" s="5">
-        <v>322463</v>
+        <v>22380</v>
       </c>
       <c r="C84" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D84" s="5">
-        <v>31165654</v>
+        <v>9256314</v>
       </c>
       <c r="E84" s="6">
-        <v>0.0106141587</v>
+        <v>0.0650187879</v>
       </c>
       <c r="F84" s="7">
-        <v>97.6856259478</v>
+        <v>442.3592493298</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -2895,19 +2895,19 @@
         <v>94</v>
       </c>
       <c r="B85" s="5">
-        <v>10991</v>
+        <v>301340</v>
       </c>
       <c r="C85" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D85" s="5">
-        <v>2839786</v>
+        <v>59499453</v>
       </c>
       <c r="E85" s="6">
-        <v>-0.0517725926</v>
+        <v>-0.0084653051</v>
       </c>
       <c r="F85" s="7">
-        <v>245.6555363479</v>
+        <v>195.7921284927</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -2915,19 +2915,19 @@
         <v>95</v>
       </c>
       <c r="B86" s="5">
-        <v>377915</v>
+        <v>322463</v>
       </c>
       <c r="C86" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D86" s="5">
-        <v>124370947</v>
+        <v>31165654</v>
       </c>
       <c r="E86" s="6">
-        <v>-0.0046118498</v>
+        <v>0.0106141587</v>
       </c>
       <c r="F86" s="7">
-        <v>327.5868912322</v>
+        <v>97.6856259478</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -2935,19 +2935,19 @@
         <v>96</v>
       </c>
       <c r="B87" s="5">
-        <v>89342</v>
+        <v>10991</v>
       </c>
       <c r="C87" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D87" s="5">
-        <v>11439213</v>
+        <v>2839786</v>
       </c>
       <c r="E87" s="6">
-        <v>0.0305751695</v>
+        <v>-0.0517725926</v>
       </c>
       <c r="F87" s="7">
-        <v>132.0767388238</v>
+        <v>245.6555363479</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -2955,19 +2955,19 @@
         <v>97</v>
       </c>
       <c r="B88" s="5">
-        <v>2724900</v>
+        <v>377915</v>
       </c>
       <c r="C88" t="s">
         <v>7</v>
       </c>
       <c r="D88" s="5">
-        <v>20330104</v>
+        <v>124370947</v>
       </c>
       <c r="E88" s="6">
-        <v>-0.0064407921</v>
+        <v>-0.0046118498</v>
       </c>
       <c r="F88" s="7">
-        <v>7.4131160777</v>
+        <v>327.5868912322</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -2975,19 +2975,19 @@
         <v>98</v>
       </c>
       <c r="B89" s="5">
-        <v>580367</v>
+        <v>89342</v>
       </c>
       <c r="C89" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D89" s="5">
-        <v>55339003</v>
+        <v>11439213</v>
       </c>
       <c r="E89" s="6">
-        <v>-0.0520723004</v>
+        <v>0.0305751695</v>
       </c>
       <c r="F89" s="7">
-        <v>90.632306799</v>
+        <v>132.0767388238</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -2995,19 +2995,19 @@
         <v>99</v>
       </c>
       <c r="B90" s="5">
-        <v>811</v>
+        <v>2724900</v>
       </c>
       <c r="C90" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D90" s="5">
-        <v>132.53</v>
+        <v>20330104</v>
       </c>
       <c r="E90" s="6">
-        <v>0.9986747</v>
+        <v>-0.0064407921</v>
       </c>
       <c r="F90" s="7">
-        <v>123.3045622688</v>
+        <v>7.4131160777</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3015,19 +3015,19 @@
         <v>100</v>
       </c>
       <c r="B91" s="5">
-        <v>120538</v>
+        <v>580367</v>
       </c>
       <c r="C91" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D91" s="5">
-        <v>26418204</v>
+        <v>55339003</v>
       </c>
       <c r="E91" s="6">
-        <v>-0.0044944487</v>
+        <v>-0.0520723004</v>
       </c>
       <c r="F91" s="7">
-        <v>218.188455093</v>
+        <v>90.632306799</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3035,19 +3035,19 @@
         <v>101</v>
       </c>
       <c r="B92" s="5">
-        <v>99720</v>
+        <v>811</v>
       </c>
       <c r="C92" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D92" s="5">
-        <v>51748739</v>
+        <v>132.53</v>
       </c>
       <c r="E92" s="6">
-        <v>0.0009895946</v>
+        <v>0.9986747</v>
       </c>
       <c r="F92" s="7">
-        <v>519.4544725231</v>
+        <v>123.3045622688</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3055,19 +3055,19 @@
         <v>102</v>
       </c>
       <c r="B93" s="5">
-        <v>10887</v>
+        <v>120538</v>
       </c>
       <c r="C93" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D93" s="5">
-        <v>1700031</v>
+        <v>26418204</v>
       </c>
       <c r="E93" s="6">
-        <v>-0.0000182353</v>
+        <v>-0.0044944487</v>
       </c>
       <c r="F93" s="7">
-        <v>156.149536144</v>
+        <v>218.188455093</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3075,19 +3075,19 @@
         <v>103</v>
       </c>
       <c r="B94" s="5">
-        <v>17818</v>
+        <v>99720</v>
       </c>
       <c r="C94" t="s">
         <v>7</v>
       </c>
       <c r="D94" s="5">
-        <v>4838782</v>
+        <v>51748739</v>
       </c>
       <c r="E94" s="6">
-        <v>0.0512192157</v>
+        <v>0.0009895946</v>
       </c>
       <c r="F94" s="7">
-        <v>286.2274104838</v>
+        <v>519.4544725231</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3095,19 +3095,19 @@
         <v>104</v>
       </c>
       <c r="B95" s="5">
-        <v>199951</v>
+        <v>10887</v>
       </c>
       <c r="C95" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D95" s="5">
-        <v>7073516</v>
+        <v>1700031</v>
       </c>
       <c r="E95" s="6">
-        <v>0.0175672222</v>
+        <v>-0.0000182353</v>
       </c>
       <c r="F95" s="7">
-        <v>36.0088221614</v>
+        <v>156.149536144</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3115,19 +3115,19 @@
         <v>105</v>
       </c>
       <c r="B96" s="5">
-        <v>236800</v>
+        <v>17818</v>
       </c>
       <c r="C96" t="s">
         <v>7</v>
       </c>
       <c r="D96" s="5">
-        <v>7664993</v>
+        <v>4838782</v>
       </c>
       <c r="E96" s="6">
-        <v>0.0045463636</v>
+        <v>0.0512192157</v>
       </c>
       <c r="F96" s="7">
-        <v>32.5168918919</v>
+        <v>286.2274104838</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3135,19 +3135,19 @@
         <v>106</v>
       </c>
       <c r="B97" s="5">
-        <v>64589</v>
+        <v>199951</v>
       </c>
       <c r="C97" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D97" s="5">
-        <v>1882396</v>
+        <v>7073516</v>
       </c>
       <c r="E97" s="6">
-        <v>0.0092652632</v>
+        <v>0.0175672222</v>
       </c>
       <c r="F97" s="7">
-        <v>29.416773754</v>
+        <v>36.0088221614</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3155,19 +3155,19 @@
         <v>107</v>
       </c>
       <c r="B98" s="5">
-        <v>10400</v>
+        <v>236800</v>
       </c>
       <c r="C98" t="s">
         <v>7</v>
       </c>
       <c r="D98" s="5">
-        <v>5733493</v>
+        <v>7664993</v>
       </c>
       <c r="E98" s="6">
-        <v>-0.1025948077</v>
+        <v>0.0045463636</v>
       </c>
       <c r="F98" s="7">
-        <v>500</v>
+        <v>32.5168918919</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3175,19 +3175,19 @@
         <v>108</v>
       </c>
       <c r="B99" s="5">
-        <v>30355</v>
+        <v>64589</v>
       </c>
       <c r="C99" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D99" s="5">
-        <v>2311472</v>
+        <v>1882396</v>
       </c>
       <c r="E99" s="6">
-        <v>-0.0049878261</v>
+        <v>0.0092652632</v>
       </c>
       <c r="F99" s="7">
-        <v>75.7700543568</v>
+        <v>29.416773754</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3195,19 +3195,19 @@
         <v>109</v>
       </c>
       <c r="B100" s="5">
-        <v>111369</v>
+        <v>10400</v>
       </c>
       <c r="C100" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D100" s="5">
-        <v>5493031</v>
+        <v>5733493</v>
       </c>
       <c r="E100" s="6">
-        <v>-0.017227963</v>
+        <v>-0.1025948077</v>
       </c>
       <c r="F100" s="7">
-        <v>48.4874606039</v>
+        <v>500</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3215,19 +3215,19 @@
         <v>110</v>
       </c>
       <c r="B101" s="5">
-        <v>1759540</v>
+        <v>30355</v>
       </c>
       <c r="C101" t="s">
         <v>11</v>
       </c>
       <c r="D101" s="5">
-        <v>7305659</v>
+        <v>2311472</v>
       </c>
       <c r="E101" s="6">
-        <v>0.0127487838</v>
+        <v>-0.0049878261</v>
       </c>
       <c r="F101" s="7">
-        <v>4.2056446571</v>
+        <v>75.7700543568</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3235,19 +3235,19 @@
         <v>111</v>
       </c>
       <c r="B102" s="5">
-        <v>160</v>
+        <v>111369</v>
       </c>
       <c r="C102" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D102" s="5">
-        <v>39.598</v>
+        <v>5493031</v>
       </c>
       <c r="E102" s="6">
-        <v>0.99901005</v>
+        <v>-0.017227963</v>
       </c>
       <c r="F102" s="7">
-        <v>250</v>
+        <v>48.4874606039</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3255,19 +3255,19 @@
         <v>112</v>
       </c>
       <c r="B103" s="5">
-        <v>65300</v>
+        <v>1759540</v>
       </c>
       <c r="C103" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D103" s="5">
-        <v>2854099</v>
+        <v>7305659</v>
       </c>
       <c r="E103" s="6">
-        <v>0.015827931</v>
+        <v>0.0127487838</v>
       </c>
       <c r="F103" s="7">
-        <v>44.4104134763</v>
+        <v>4.2056446571</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3275,19 +3275,19 @@
         <v>113</v>
       </c>
       <c r="B104" s="5">
-        <v>2586</v>
+        <v>160</v>
       </c>
       <c r="C104" t="s">
         <v>9</v>
       </c>
       <c r="D104" s="5">
-        <v>665.098</v>
+        <v>39.598</v>
       </c>
       <c r="E104" s="6">
-        <v>0.99904986</v>
+        <v>0.99901005</v>
       </c>
       <c r="F104" s="7">
-        <v>270.6883217324</v>
+        <v>250</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3295,19 +3295,19 @@
         <v>114</v>
       </c>
       <c r="B105" s="5">
-        <v>587041</v>
+        <v>65300</v>
       </c>
       <c r="C105" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D105" s="5">
-        <v>31195932</v>
+        <v>2854099</v>
       </c>
       <c r="E105" s="6">
-        <v>-0.0128549351</v>
+        <v>0.015827931</v>
       </c>
       <c r="F105" s="7">
-        <v>52.4665227812</v>
+        <v>44.4104134763</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3315,19 +3315,19 @@
         <v>115</v>
       </c>
       <c r="B106" s="5">
-        <v>118484</v>
+        <v>2586</v>
       </c>
       <c r="C106" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D106" s="5">
-        <v>21104482</v>
+        <v>665.098</v>
       </c>
       <c r="E106" s="6">
-        <v>-0.0396296552</v>
+        <v>0.99904986</v>
       </c>
       <c r="F106" s="7">
-        <v>171.3311501975</v>
+        <v>270.6883217324</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3335,19 +3335,19 @@
         <v>116</v>
       </c>
       <c r="B107" s="5">
-        <v>329847</v>
+        <v>587041</v>
       </c>
       <c r="C107" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D107" s="5">
-        <v>35126298</v>
+        <v>31195932</v>
       </c>
       <c r="E107" s="6">
-        <v>-0.0270847368</v>
+        <v>-0.0128549351</v>
       </c>
       <c r="F107" s="7">
-        <v>103.684435511</v>
+        <v>52.4665227812</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3355,19 +3355,19 @@
         <v>117</v>
       </c>
       <c r="B108" s="5">
-        <v>298</v>
+        <v>118484</v>
       </c>
       <c r="C108" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D108" s="5">
-        <v>525.994</v>
+        <v>21104482</v>
       </c>
       <c r="E108" s="6">
-        <v>0.9991233433</v>
+        <v>-0.0396296552</v>
       </c>
       <c r="F108" s="7">
-        <v>2013.4228187919</v>
+        <v>171.3311501975</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3375,19 +3375,19 @@
         <v>118</v>
       </c>
       <c r="B109" s="5">
-        <v>1240192</v>
+        <v>329847</v>
       </c>
       <c r="C109" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D109" s="5">
-        <v>23769127</v>
+        <v>35126298</v>
       </c>
       <c r="E109" s="6">
-        <v>-0.0379531441</v>
+        <v>-0.0270847368</v>
       </c>
       <c r="F109" s="7">
-        <v>18.4648828568</v>
+        <v>103.684435511</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3395,19 +3395,19 @@
         <v>119</v>
       </c>
       <c r="B110" s="5">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="C110" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D110" s="5">
-        <v>532.956</v>
+        <v>525.994</v>
       </c>
       <c r="E110" s="6">
-        <v>0.99911174</v>
+        <v>0.9991233433</v>
       </c>
       <c r="F110" s="7">
-        <v>1898.7341772152</v>
+        <v>2013.4228187919</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3415,19 +3415,19 @@
         <v>120</v>
       </c>
       <c r="B111" s="5">
-        <v>181</v>
+        <v>1240192</v>
       </c>
       <c r="C111" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D111" s="5">
-        <v>38.827</v>
+        <v>23769127</v>
       </c>
       <c r="E111" s="6">
-        <v>0.99922346</v>
+        <v>-0.0379531441</v>
       </c>
       <c r="F111" s="7">
-        <v>276.2430939227</v>
+        <v>18.4648828568</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3435,19 +3435,19 @@
         <v>121</v>
       </c>
       <c r="B112" s="5">
-        <v>1030700</v>
+        <v>316</v>
       </c>
       <c r="C112" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D112" s="5">
-        <v>5022441</v>
+        <v>532.956</v>
       </c>
       <c r="E112" s="6">
-        <v>-0.091835</v>
+        <v>0.99911174</v>
       </c>
       <c r="F112" s="7">
-        <v>4.46298632</v>
+        <v>1898.7341772152</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3455,19 +3455,19 @@
         <v>122</v>
       </c>
       <c r="B113" s="5">
-        <v>2103</v>
+        <v>181</v>
       </c>
       <c r="C113" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D113" s="5">
-        <v>1273588</v>
+        <v>38.827</v>
       </c>
       <c r="E113" s="6">
-        <v>0.0203169231</v>
+        <v>0.99922346</v>
       </c>
       <c r="F113" s="7">
-        <v>618.1645268664</v>
+        <v>276.2430939227</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3475,19 +3475,19 @@
         <v>123</v>
       </c>
       <c r="B114" s="5">
-        <v>1964375</v>
+        <v>1030700</v>
       </c>
       <c r="C114" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D114" s="5">
-        <v>129739759</v>
+        <v>5022441</v>
       </c>
       <c r="E114" s="6">
-        <v>-0.0026256491</v>
+        <v>-0.091835</v>
       </c>
       <c r="F114" s="7">
-        <v>65.8733693923</v>
+        <v>4.46298632</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3495,19 +3495,19 @@
         <v>124</v>
       </c>
       <c r="B115" s="5">
-        <v>702</v>
+        <v>2103</v>
       </c>
       <c r="C115" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D115" s="5">
-        <v>112.63</v>
+        <v>1273588</v>
       </c>
       <c r="E115" s="6">
-        <v>0.9988737</v>
+        <v>0.0203169231</v>
       </c>
       <c r="F115" s="7">
-        <v>142.4501424501</v>
+        <v>618.1645268664</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3515,19 +3515,19 @@
         <v>125</v>
       </c>
       <c r="B116" s="5">
-        <v>33851</v>
+        <v>1964375</v>
       </c>
       <c r="C116" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D116" s="5">
-        <v>3067070</v>
+        <v>129739759</v>
       </c>
       <c r="E116" s="6">
-        <v>0.1236942857</v>
+        <v>-0.0026256491</v>
       </c>
       <c r="F116" s="7">
-        <v>103.3942867271</v>
+        <v>65.8733693923</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3535,19 +3535,19 @@
         <v>126</v>
       </c>
       <c r="B117" s="5">
-        <v>203</v>
+        <v>33851</v>
       </c>
       <c r="C117" t="s">
         <v>9</v>
       </c>
       <c r="D117" s="5">
-        <v>38.956</v>
+        <v>3067070</v>
       </c>
       <c r="E117" s="6">
-        <v>0.9990261</v>
+        <v>0.1236942857</v>
       </c>
       <c r="F117" s="7">
-        <v>197.0443349754</v>
+        <v>103.3942867271</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3555,19 +3555,19 @@
         <v>127</v>
       </c>
       <c r="B118" s="5">
-        <v>1564116</v>
+        <v>203</v>
       </c>
       <c r="C118" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D118" s="5">
-        <v>3431932</v>
+        <v>38.956</v>
       </c>
       <c r="E118" s="6">
-        <v>-0.0093917647</v>
+        <v>0.9990261</v>
       </c>
       <c r="F118" s="7">
-        <v>2.1737518189</v>
+        <v>197.0443349754</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3575,19 +3575,19 @@
         <v>128</v>
       </c>
       <c r="B119" s="5">
-        <v>13812</v>
+        <v>1564116</v>
       </c>
       <c r="C119" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D119" s="5">
-        <v>633.552</v>
+        <v>3431932</v>
       </c>
       <c r="E119" s="6">
-        <v>0.99894408</v>
+        <v>-0.0093917647</v>
       </c>
       <c r="F119" s="7">
-        <v>43.4404865334</v>
+        <v>2.1737518189</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3595,19 +3595,19 @@
         <v>129</v>
       </c>
       <c r="B120" s="5">
-        <v>446550</v>
+        <v>13812</v>
       </c>
       <c r="C120" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D120" s="5">
-        <v>37712505</v>
+        <v>633.552</v>
       </c>
       <c r="E120" s="6">
-        <v>-0.0083557487</v>
+        <v>0.99894408</v>
       </c>
       <c r="F120" s="7">
-        <v>83.7532191244</v>
+        <v>43.4404865334</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3615,19 +3615,19 @@
         <v>130</v>
       </c>
       <c r="B121" s="5">
-        <v>799380</v>
+        <v>446550</v>
       </c>
       <c r="C121" t="s">
         <v>11</v>
       </c>
       <c r="D121" s="5">
-        <v>33635160</v>
+        <v>37712505</v>
       </c>
       <c r="E121" s="6">
-        <v>-0.0131072289</v>
+        <v>-0.0083557487</v>
       </c>
       <c r="F121" s="7">
-        <v>41.5321874453</v>
+        <v>83.7532191244</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3635,19 +3635,19 @@
         <v>131</v>
       </c>
       <c r="B122" s="5">
-        <v>676578</v>
+        <v>799380</v>
       </c>
       <c r="C122" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D122" s="5">
-        <v>54133798</v>
+        <v>33635160</v>
       </c>
       <c r="E122" s="6">
-        <v>0.0585426435</v>
+        <v>-0.0131072289</v>
       </c>
       <c r="F122" s="7">
-        <v>84.9865056209</v>
+        <v>41.5321874453</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3655,19 +3655,19 @@
         <v>132</v>
       </c>
       <c r="B123" s="5">
-        <v>824292</v>
+        <v>676578</v>
       </c>
       <c r="C123" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D123" s="5">
-        <v>2963095</v>
+        <v>54133798</v>
       </c>
       <c r="E123" s="6">
-        <v>-0.0582482143</v>
+        <v>0.0585426435</v>
       </c>
       <c r="F123" s="7">
-        <v>3.3968545127</v>
+        <v>84.9865056209</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3675,59 +3675,53 @@
         <v>133</v>
       </c>
       <c r="B124" s="5">
-        <v>21</v>
+        <v>824292</v>
       </c>
       <c r="C124" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D124" s="5">
-        <v>11.875</v>
+        <v>2963095</v>
       </c>
       <c r="E124" s="6">
-        <v>0.9988125</v>
+        <v>-0.0582482143</v>
       </c>
       <c r="F124" s="7">
-        <v>476.1904761905</v>
+        <v>3.3968545127</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>134</v>
       </c>
-      <c r="B125" s="5">
-        <v>147181</v>
-      </c>
+      <c r="B125" s="5"/>
       <c r="C125" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D125" s="5">
-        <v>29964614</v>
-      </c>
-      <c r="E125" s="6">
-        <v>0.0011795333</v>
-      </c>
-      <c r="F125" s="7">
-        <v>203.8306574898</v>
-      </c>
+        <v>11.875</v>
+      </c>
+      <c r="E125" s="6"/>
+      <c r="F125" s="7"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>135</v>
       </c>
       <c r="B126" s="5">
-        <v>41543</v>
+        <v>147181</v>
       </c>
       <c r="C126" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D126" s="5">
-        <v>18092524</v>
+        <v>29964614</v>
       </c>
       <c r="E126" s="6">
-        <v>-0.0051402222</v>
+        <v>0.0011795333</v>
       </c>
       <c r="F126" s="7">
-        <v>433.2859928267</v>
+        <v>203.8306574898</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -3735,19 +3729,19 @@
         <v>136</v>
       </c>
       <c r="B127" s="5">
-        <v>267710</v>
+        <v>41543</v>
       </c>
       <c r="C127" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D127" s="5">
-        <v>5172836</v>
+        <v>18092524</v>
       </c>
       <c r="E127" s="6">
-        <v>0.0420674074</v>
+        <v>-0.0051402222</v>
       </c>
       <c r="F127" s="7">
-        <v>20.171080647</v>
+        <v>433.2859928267</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -3755,19 +3749,19 @@
         <v>137</v>
       </c>
       <c r="B128" s="5">
-        <v>130730</v>
+        <v>267710</v>
       </c>
       <c r="C128" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D128" s="5">
-        <v>6823613</v>
+        <v>5172836</v>
       </c>
       <c r="E128" s="6">
-        <v>0.0110705797</v>
+        <v>0.0420674074</v>
       </c>
       <c r="F128" s="7">
-        <v>52.7805400444</v>
+        <v>20.171080647</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -3775,19 +3769,19 @@
         <v>138</v>
       </c>
       <c r="B129" s="5">
-        <v>1267000</v>
+        <v>130730</v>
       </c>
       <c r="C129" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D129" s="5">
-        <v>26159867</v>
+        <v>6823613</v>
       </c>
       <c r="E129" s="6">
-        <v>0.005328251</v>
+        <v>0.0110705797</v>
       </c>
       <c r="F129" s="7">
-        <v>20.7576953433</v>
+        <v>52.7805400444</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -3795,19 +3789,19 @@
         <v>139</v>
       </c>
       <c r="B130" s="5">
-        <v>923768</v>
+        <v>1267000</v>
       </c>
       <c r="C130" t="s">
         <v>11</v>
       </c>
       <c r="D130" s="5">
-        <v>227882945</v>
+        <v>26159867</v>
       </c>
       <c r="E130" s="6">
-        <v>-0.0003641133</v>
+        <v>0.005328251</v>
       </c>
       <c r="F130" s="7">
-        <v>246.5987130968</v>
+        <v>20.7576953433</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -3815,19 +3809,19 @@
         <v>140</v>
       </c>
       <c r="B131" s="5">
-        <v>25713</v>
+        <v>923768</v>
       </c>
       <c r="C131" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D131" s="5">
-        <v>1831802</v>
+        <v>227882945</v>
       </c>
       <c r="E131" s="6">
-        <v>-0.0176677778</v>
+        <v>-0.0003641133</v>
       </c>
       <c r="F131" s="7">
-        <v>70.003500175</v>
+        <v>246.5987130968</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -3835,19 +3829,19 @@
         <v>141</v>
       </c>
       <c r="B132" s="5">
-        <v>323802</v>
+        <v>260</v>
       </c>
       <c r="C132" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D132" s="5">
-        <v>5519167</v>
+        <v>1.817</v>
       </c>
       <c r="E132" s="6">
-        <v>0.0144344643</v>
+        <v>0.9985215622</v>
       </c>
       <c r="F132" s="7">
-        <v>17.2945194903</v>
+        <v>4.7269230769</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -3855,19 +3849,19 @@
         <v>142</v>
       </c>
       <c r="B133" s="5">
-        <v>309500</v>
+        <v>25713</v>
       </c>
       <c r="C133" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D133" s="5">
-        <v>5049269</v>
+        <v>1831802</v>
       </c>
       <c r="E133" s="6">
-        <v>0.0289867308</v>
+        <v>-0.0176677778</v>
       </c>
       <c r="F133" s="7">
-        <v>16.8012924071</v>
+        <v>70.003500175</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -3875,19 +3869,19 @@
         <v>143</v>
       </c>
       <c r="B134" s="5">
-        <v>796095</v>
+        <v>323802</v>
       </c>
       <c r="C134" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D134" s="5">
-        <v>247504495</v>
+        <v>5519167</v>
       </c>
       <c r="E134" s="6">
-        <v>-0.0164455647</v>
+        <v>0.0144344643</v>
       </c>
       <c r="F134" s="7">
-        <v>305.8680182642</v>
+        <v>17.2945194903</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -3895,19 +3889,19 @@
         <v>144</v>
       </c>
       <c r="B135" s="5">
-        <v>459</v>
+        <v>309500</v>
       </c>
       <c r="C135" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D135" s="5">
-        <v>17.727</v>
+        <v>5049269</v>
       </c>
       <c r="E135" s="6">
-        <v>0.99911365</v>
+        <v>0.0289867308</v>
       </c>
       <c r="F135" s="7">
-        <v>43.5729847495</v>
+        <v>16.8012924071</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -3915,19 +3909,19 @@
         <v>145</v>
       </c>
       <c r="B136" s="5">
-        <v>6220</v>
+        <v>796095</v>
       </c>
       <c r="C136" t="s">
         <v>7</v>
       </c>
       <c r="D136" s="5">
-        <v>5409202</v>
+        <v>247504495</v>
       </c>
       <c r="E136" s="6">
-        <v>-0.0017040741</v>
+        <v>-0.0164455647</v>
       </c>
       <c r="F136" s="7">
-        <v>868.1672025723</v>
+        <v>305.8680182642</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -3935,19 +3929,19 @@
         <v>146</v>
       </c>
       <c r="B137" s="5">
-        <v>75420</v>
+        <v>459</v>
       </c>
       <c r="C137" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D137" s="5">
-        <v>4458759</v>
+        <v>17.727</v>
       </c>
       <c r="E137" s="6">
-        <v>0.0091646667</v>
+        <v>0.99911365</v>
       </c>
       <c r="F137" s="7">
-        <v>59.6658711217</v>
+        <v>43.5729847495</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -3955,19 +3949,19 @@
         <v>147</v>
       </c>
       <c r="B138" s="5">
-        <v>462840</v>
+        <v>6220</v>
       </c>
       <c r="C138" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D138" s="5">
-        <v>10389635</v>
+        <v>5409202</v>
       </c>
       <c r="E138" s="6">
-        <v>-0.0710963918</v>
+        <v>-0.0017040741</v>
       </c>
       <c r="F138" s="7">
-        <v>20.9575663296</v>
+        <v>868.1672025723</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -3975,19 +3969,19 @@
         <v>148</v>
       </c>
       <c r="B139" s="5">
-        <v>406752</v>
+        <v>75420</v>
       </c>
       <c r="C139" t="s">
         <v>15</v>
       </c>
       <c r="D139" s="5">
-        <v>6844146</v>
+        <v>4458759</v>
       </c>
       <c r="E139" s="6">
-        <v>0.0080947826</v>
+        <v>0.0091646667</v>
       </c>
       <c r="F139" s="7">
-        <v>16.9636535284</v>
+        <v>59.6658711217</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -3995,19 +3989,19 @@
         <v>149</v>
       </c>
       <c r="B140" s="5">
-        <v>1285216</v>
+        <v>462840</v>
       </c>
       <c r="C140" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D140" s="5">
-        <v>33845617</v>
+        <v>10389635</v>
       </c>
       <c r="E140" s="6">
-        <v>0.0045406765</v>
+        <v>-0.0710963918</v>
       </c>
       <c r="F140" s="7">
-        <v>26.4546971093</v>
+        <v>20.9575663296</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4015,19 +4009,19 @@
         <v>150</v>
       </c>
       <c r="B141" s="5">
-        <v>299000</v>
+        <v>406752</v>
       </c>
       <c r="C141" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D141" s="5">
-        <v>114891199</v>
+        <v>6844146</v>
       </c>
       <c r="E141" s="6">
-        <v>-0.0042936976</v>
+        <v>0.0080947826</v>
       </c>
       <c r="F141" s="7">
-        <v>382.6086956522</v>
+        <v>16.9636535284</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4035,19 +4029,19 @@
         <v>151</v>
       </c>
       <c r="B142" s="5">
-        <v>312685</v>
+        <v>1285216</v>
       </c>
       <c r="C142" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D142" s="5">
-        <v>38762844</v>
+        <v>33845617</v>
       </c>
       <c r="E142" s="6">
-        <v>-0.0309267021</v>
+        <v>0.0045406765</v>
       </c>
       <c r="F142" s="7">
-        <v>120.2488127029</v>
+        <v>26.4546971093</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4055,19 +4049,19 @@
         <v>152</v>
       </c>
       <c r="B143" s="5">
-        <v>92090</v>
+        <v>299000</v>
       </c>
       <c r="C143" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D143" s="5">
-        <v>10430738</v>
+        <v>114891199</v>
       </c>
       <c r="E143" s="6">
-        <v>0.0251646729</v>
+        <v>-0.0042936976</v>
       </c>
       <c r="F143" s="7">
-        <v>116.1906830275</v>
+        <v>382.6086956522</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4075,19 +4069,19 @@
         <v>153</v>
       </c>
       <c r="B144" s="5">
-        <v>11586</v>
+        <v>312685</v>
       </c>
       <c r="C144" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D144" s="5">
-        <v>2979082</v>
+        <v>38762844</v>
       </c>
       <c r="E144" s="6">
-        <v>0.069036875</v>
+        <v>-0.0309267021</v>
       </c>
       <c r="F144" s="7">
-        <v>276.1954082513</v>
+        <v>120.2488127029</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4095,19 +4089,19 @@
         <v>154</v>
       </c>
       <c r="B145" s="5">
-        <v>238391</v>
+        <v>92090</v>
       </c>
       <c r="C145" t="s">
         <v>9</v>
       </c>
       <c r="D145" s="5">
-        <v>19118479</v>
+        <v>10430738</v>
       </c>
       <c r="E145" s="6">
-        <v>-0.0009674869</v>
+        <v>0.0251646729</v>
       </c>
       <c r="F145" s="7">
-        <v>80.1204743468</v>
+        <v>116.1906830275</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4115,19 +4109,19 @@
         <v>155</v>
       </c>
       <c r="B146" s="5">
-        <v>17098242</v>
+        <v>11586</v>
       </c>
       <c r="C146" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D146" s="5">
-        <v>145440500</v>
+        <v>2979082</v>
       </c>
       <c r="E146" s="6">
-        <v>0.0038321918</v>
+        <v>0.069036875</v>
       </c>
       <c r="F146" s="7">
-        <v>8.5388895537</v>
+        <v>276.1954082513</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4135,19 +4129,19 @@
         <v>156</v>
       </c>
       <c r="B147" s="5">
-        <v>26338</v>
+        <v>238391</v>
       </c>
       <c r="C147" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D147" s="5">
-        <v>13954471</v>
+        <v>19118479</v>
       </c>
       <c r="E147" s="6">
-        <v>-0.0111935507</v>
+        <v>-0.0009674869</v>
       </c>
       <c r="F147" s="7">
-        <v>523.957779634</v>
+        <v>80.1204743468</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4155,19 +4149,19 @@
         <v>157</v>
       </c>
       <c r="B148" s="5">
-        <v>261</v>
+        <v>17098242</v>
       </c>
       <c r="C148" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D148" s="5">
-        <v>46.758</v>
+        <v>145440500</v>
       </c>
       <c r="E148" s="6">
-        <v>0.99906484</v>
+        <v>0.0038321918</v>
       </c>
       <c r="F148" s="7">
-        <v>191.5708812261</v>
+        <v>8.5388895537</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4175,19 +4169,19 @@
         <v>158</v>
       </c>
       <c r="B149" s="5">
-        <v>616</v>
+        <v>26338</v>
       </c>
       <c r="C149" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D149" s="5">
-        <v>179.285</v>
+        <v>13954471</v>
       </c>
       <c r="E149" s="6">
-        <v>0.999103575</v>
+        <v>-0.0111935507</v>
       </c>
       <c r="F149" s="7">
-        <v>324.6753246753</v>
+        <v>523.957779634</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4195,19 +4189,19 @@
         <v>159</v>
       </c>
       <c r="B150" s="5">
-        <v>389</v>
+        <v>261</v>
       </c>
       <c r="C150" t="s">
         <v>15</v>
       </c>
       <c r="D150" s="5">
-        <v>101.323</v>
+        <v>46.758</v>
       </c>
       <c r="E150" s="6">
-        <v>0.99898677</v>
+        <v>0.99906484</v>
       </c>
       <c r="F150" s="7">
-        <v>257.0694087404</v>
+        <v>191.5708812261</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -4215,19 +4209,19 @@
         <v>160</v>
       </c>
       <c r="B151" s="5">
-        <v>2831</v>
+        <v>616</v>
       </c>
       <c r="C151" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D151" s="5">
-        <v>216.663</v>
+        <v>179.285</v>
       </c>
       <c r="E151" s="6">
-        <v>0.998916685</v>
+        <v>0.999103575</v>
       </c>
       <c r="F151" s="7">
-        <v>70.6464146945</v>
+        <v>324.6753246753</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4235,19 +4229,19 @@
         <v>161</v>
       </c>
       <c r="B152" s="5">
-        <v>61</v>
+        <v>389</v>
       </c>
       <c r="C152" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D152" s="5">
-        <v>33.733</v>
+        <v>101.323</v>
       </c>
       <c r="E152" s="6">
-        <v>0.999156675</v>
+        <v>0.99898677</v>
       </c>
       <c r="F152" s="7">
-        <v>655.737704918</v>
+        <v>257.0694087404</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4255,19 +4249,19 @@
         <v>162</v>
       </c>
       <c r="B153" s="5">
-        <v>2149690</v>
+        <v>2831</v>
       </c>
       <c r="C153" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D153" s="5">
-        <v>32264292</v>
+        <v>216.663</v>
       </c>
       <c r="E153" s="6">
-        <v>0.0807894017</v>
+        <v>0.998916685</v>
       </c>
       <c r="F153" s="7">
-        <v>16.3279356558</v>
+        <v>70.6464146945</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -4275,19 +4269,19 @@
         <v>163</v>
       </c>
       <c r="B154" s="5">
-        <v>196722</v>
+        <v>61</v>
       </c>
       <c r="C154" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D154" s="5">
-        <v>18077573</v>
+        <v>33.733</v>
       </c>
       <c r="E154" s="6">
-        <v>0.0228338919</v>
+        <v>0.999156675</v>
       </c>
       <c r="F154" s="7">
-        <v>94.041337522</v>
+        <v>655.737704918</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -4295,19 +4289,19 @@
         <v>164</v>
       </c>
       <c r="B155" s="5">
-        <v>77474</v>
+        <v>2149690</v>
       </c>
       <c r="C155" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D155" s="5">
-        <v>6773201</v>
+        <v>32264292</v>
       </c>
       <c r="E155" s="6">
-        <v>-0.0262425758</v>
+        <v>0.0807894017</v>
       </c>
       <c r="F155" s="7">
-        <v>85.18987015</v>
+        <v>16.3279356558</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4315,19 +4309,19 @@
         <v>165</v>
       </c>
       <c r="B156" s="5">
-        <v>455</v>
+        <v>196722</v>
       </c>
       <c r="C156" t="s">
         <v>11</v>
       </c>
       <c r="D156" s="5">
-        <v>127.951</v>
+        <v>18077573</v>
       </c>
       <c r="E156" s="6">
-        <v>0.99872049</v>
+        <v>0.0228338919</v>
       </c>
       <c r="F156" s="7">
-        <v>219.7802197802</v>
+        <v>94.041337522</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4335,19 +4329,19 @@
         <v>166</v>
       </c>
       <c r="B157" s="5">
-        <v>71740</v>
+        <v>77474</v>
       </c>
       <c r="C157" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D157" s="5">
-        <v>8460512</v>
+        <v>6773201</v>
       </c>
       <c r="E157" s="6">
-        <v>0.0162195349</v>
+        <v>-0.0262425758</v>
       </c>
       <c r="F157" s="7">
-        <v>119.8773348202</v>
+        <v>85.18987015</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -4355,19 +4349,19 @@
         <v>167</v>
       </c>
       <c r="B158" s="5">
-        <v>697</v>
+        <v>455</v>
       </c>
       <c r="C158" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D158" s="5">
-        <v>5789090</v>
+        <v>127.951</v>
       </c>
       <c r="E158" s="6">
-        <v>0.0662758065</v>
+        <v>0.99872049</v>
       </c>
       <c r="F158" s="7">
-        <v>8895.2654232425</v>
+        <v>219.7802197802</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -4375,19 +4369,19 @@
         <v>168</v>
       </c>
       <c r="B159" s="5">
-        <v>49035</v>
+        <v>71740</v>
       </c>
       <c r="C159" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D159" s="5">
-        <v>5518055</v>
+        <v>8460512</v>
       </c>
       <c r="E159" s="6">
-        <v>-0.021862037</v>
+        <v>0.0162195349</v>
       </c>
       <c r="F159" s="7">
-        <v>110.1254206179</v>
+        <v>119.8773348202</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4395,19 +4389,19 @@
         <v>169</v>
       </c>
       <c r="B160" s="5">
-        <v>20273</v>
+        <v>697</v>
       </c>
       <c r="C160" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D160" s="5">
-        <v>2118396</v>
+        <v>5789090</v>
       </c>
       <c r="E160" s="6">
-        <v>-0.00876</v>
+        <v>0.0662758065</v>
       </c>
       <c r="F160" s="7">
-        <v>103.5860504119</v>
+        <v>8895.2654232425</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4415,19 +4409,19 @@
         <v>170</v>
       </c>
       <c r="B161" s="5">
-        <v>28896</v>
+        <v>49035</v>
       </c>
       <c r="C161" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D161" s="5">
-        <v>800.005</v>
+        <v>5518055</v>
       </c>
       <c r="E161" s="6">
-        <v>0.9989999938</v>
+        <v>-0.021862037</v>
       </c>
       <c r="F161" s="7">
-        <v>27.6854928018</v>
+        <v>110.1254206179</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4435,19 +4429,19 @@
         <v>171</v>
       </c>
       <c r="B162" s="5">
-        <v>637657</v>
+        <v>20273</v>
       </c>
       <c r="C162" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D162" s="5">
-        <v>18358615</v>
+        <v>2118396</v>
       </c>
       <c r="E162" s="6">
-        <v>0.0337571053</v>
+        <v>-0.00876</v>
       </c>
       <c r="F162" s="7">
-        <v>29.7965834296</v>
+        <v>103.5860504119</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4455,19 +4449,19 @@
         <v>172</v>
       </c>
       <c r="B163" s="5">
-        <v>1219090</v>
+        <v>28896</v>
       </c>
       <c r="C163" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D163" s="5">
-        <v>63212384</v>
+        <v>800.005</v>
       </c>
       <c r="E163" s="6">
-        <v>-0.0033711746</v>
+        <v>0.9989999938</v>
       </c>
       <c r="F163" s="7">
-        <v>51.6778908858</v>
+        <v>27.6854928018</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4475,19 +4469,19 @@
         <v>173</v>
       </c>
       <c r="B164" s="5">
-        <v>644329</v>
+        <v>637657</v>
       </c>
       <c r="C164" t="s">
         <v>11</v>
       </c>
       <c r="D164" s="5">
-        <v>11483374</v>
+        <v>18358615</v>
       </c>
       <c r="E164" s="6">
-        <v>0.0350105882</v>
+        <v>0.0337571053</v>
       </c>
       <c r="F164" s="7">
-        <v>18.4688257086</v>
+        <v>29.7965834296</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -4495,19 +4489,19 @@
         <v>174</v>
       </c>
       <c r="B165" s="5">
-        <v>505370</v>
+        <v>1219090</v>
       </c>
       <c r="C165" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D165" s="5">
-        <v>47911579</v>
+        <v>63212384</v>
       </c>
       <c r="E165" s="6">
-        <v>0.0182053484</v>
+        <v>-0.0033711746</v>
       </c>
       <c r="F165" s="7">
-        <v>96.5629143004</v>
+        <v>51.6778908858</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -4515,19 +4509,19 @@
         <v>175</v>
       </c>
       <c r="B166" s="5">
-        <v>65610</v>
+        <v>644329</v>
       </c>
       <c r="C166" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D166" s="5">
-        <v>22971617</v>
+        <v>11483374</v>
       </c>
       <c r="E166" s="6">
-        <v>-0.0489322831</v>
+        <v>0.0350105882</v>
       </c>
       <c r="F166" s="7">
-        <v>333.7905807042</v>
+        <v>18.4688257086</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -4535,19 +4529,19 @@
         <v>176</v>
       </c>
       <c r="B167" s="5">
-        <v>1861484</v>
+        <v>505370</v>
       </c>
       <c r="C167" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D167" s="5">
-        <v>50042791</v>
+        <v>47911579</v>
       </c>
       <c r="E167" s="6">
-        <v>0.0070874802</v>
+        <v>0.0182053484</v>
       </c>
       <c r="F167" s="7">
-        <v>27.0751722819</v>
+        <v>96.5629143004</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -4555,19 +4549,19 @@
         <v>177</v>
       </c>
       <c r="B168" s="5">
-        <v>163820</v>
+        <v>65610</v>
       </c>
       <c r="C168" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D168" s="5">
-        <v>628.886</v>
+        <v>22971617</v>
       </c>
       <c r="E168" s="6">
-        <v>0.9991015914</v>
+        <v>-0.0489322831</v>
       </c>
       <c r="F168" s="7">
-        <v>4.2729825418</v>
+        <v>333.7905807042</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -4575,19 +4569,19 @@
         <v>178</v>
       </c>
       <c r="B169" s="5">
-        <v>450295</v>
+        <v>1861484</v>
       </c>
       <c r="C169" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D169" s="5">
-        <v>10551494</v>
+        <v>50042791</v>
       </c>
       <c r="E169" s="6">
-        <v>0.0045760377</v>
+        <v>0.0070874802</v>
       </c>
       <c r="F169" s="7">
-        <v>23.5401236967</v>
+        <v>27.0751722819</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -4595,19 +4589,19 @@
         <v>179</v>
       </c>
       <c r="B170" s="5">
-        <v>41277</v>
+        <v>163820</v>
       </c>
       <c r="C170" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D170" s="5">
-        <v>8870561</v>
+        <v>628.886</v>
       </c>
       <c r="E170" s="6">
-        <v>0.0143821111</v>
+        <v>0.9991015914</v>
       </c>
       <c r="F170" s="7">
-        <v>218.0391016789</v>
+        <v>4.2729825418</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -4615,19 +4609,19 @@
         <v>180</v>
       </c>
       <c r="B171" s="5">
-        <v>185180</v>
+        <v>450295</v>
       </c>
       <c r="C171" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D171" s="5">
-        <v>23594623</v>
+        <v>10551494</v>
       </c>
       <c r="E171" s="6">
-        <v>0.0447521053</v>
+        <v>0.0045760377</v>
       </c>
       <c r="F171" s="7">
-        <v>133.3837347446</v>
+        <v>23.5401236967</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -4635,19 +4629,19 @@
         <v>181</v>
       </c>
       <c r="B172" s="5">
-        <v>964</v>
+        <v>41277</v>
       </c>
       <c r="C172" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D172" s="5">
-        <v>230.871</v>
+        <v>8870561</v>
       </c>
       <c r="E172" s="6">
-        <v>0.998845645</v>
+        <v>0.0143821111</v>
       </c>
       <c r="F172" s="7">
-        <v>207.468879668</v>
+        <v>218.0391016789</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -4655,19 +4649,19 @@
         <v>182</v>
       </c>
       <c r="B173" s="5">
-        <v>35980</v>
+        <v>185180</v>
       </c>
       <c r="C173" t="s">
         <v>7</v>
       </c>
       <c r="D173" s="5">
-        <v>23317145</v>
+        <v>23594623</v>
       </c>
       <c r="E173" s="6">
-        <v>0.0077810638</v>
+        <v>0.0447521053</v>
       </c>
       <c r="F173" s="7">
-        <v>653.1406336854</v>
+        <v>133.3837347446</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -4675,19 +4669,19 @@
         <v>183</v>
       </c>
       <c r="B174" s="5">
-        <v>143100</v>
+        <v>964</v>
       </c>
       <c r="C174" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D174" s="5">
-        <v>10389799</v>
+        <v>230.871</v>
       </c>
       <c r="E174" s="6">
-        <v>-0.0087183495</v>
+        <v>0.998845645</v>
       </c>
       <c r="F174" s="7">
-        <v>71.9776380154</v>
+        <v>207.468879668</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -4695,19 +4689,19 @@
         <v>184</v>
       </c>
       <c r="B175" s="5">
-        <v>947300</v>
+        <v>35980</v>
       </c>
       <c r="C175" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D175" s="5">
-        <v>66617606</v>
+        <v>23317145</v>
       </c>
       <c r="E175" s="6">
-        <v>0.0288978717</v>
+        <v>0.0077810638</v>
       </c>
       <c r="F175" s="7">
-        <v>72.4163411802</v>
+        <v>653.1406336854</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -4715,19 +4709,19 @@
         <v>185</v>
       </c>
       <c r="B176" s="5">
-        <v>513120</v>
+        <v>143100</v>
       </c>
       <c r="C176" t="s">
         <v>7</v>
       </c>
       <c r="D176" s="5">
-        <v>71702435</v>
+        <v>10389799</v>
       </c>
       <c r="E176" s="6">
-        <v>-0.0000339609</v>
+        <v>-0.0087183495</v>
       </c>
       <c r="F176" s="7">
-        <v>139.7333956969</v>
+        <v>71.9776380154</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -4735,19 +4729,19 @@
         <v>186</v>
       </c>
       <c r="B177" s="5">
-        <v>14950</v>
+        <v>947300</v>
       </c>
       <c r="C177" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D177" s="5">
-        <v>1384286</v>
+        <v>66617606</v>
       </c>
       <c r="E177" s="6">
-        <v>0</v>
+        <v>0.0288978717</v>
       </c>
       <c r="F177" s="7">
-        <v>92.5943812709</v>
+        <v>72.4163411802</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -4755,19 +4749,19 @@
         <v>187</v>
       </c>
       <c r="B178" s="5">
-        <v>56785</v>
+        <v>513120</v>
       </c>
       <c r="C178" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D178" s="5">
-        <v>9304337</v>
+        <v>71702435</v>
       </c>
       <c r="E178" s="6">
-        <v>-0.0946278824</v>
+        <v>-0.0000339609</v>
       </c>
       <c r="F178" s="7">
-        <v>149.6874174518</v>
+        <v>139.7333956969</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -4775,19 +4769,19 @@
         <v>188</v>
       </c>
       <c r="B179" s="5">
-        <v>747</v>
+        <v>14950</v>
       </c>
       <c r="C179" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D179" s="5">
-        <v>104.597</v>
+        <v>1384286</v>
       </c>
       <c r="E179" s="6">
-        <v>0.99895403</v>
+        <v>0</v>
       </c>
       <c r="F179" s="7">
-        <v>133.8688085676</v>
+        <v>92.5943812709</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -4795,19 +4789,19 @@
         <v>189</v>
       </c>
       <c r="B180" s="5">
-        <v>5128</v>
+        <v>56785</v>
       </c>
       <c r="C180" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D180" s="5">
-        <v>1502932</v>
+        <v>9304337</v>
       </c>
       <c r="E180" s="6">
-        <v>-0.0735228571</v>
+        <v>-0.0946278824</v>
       </c>
       <c r="F180" s="7">
-        <v>273.0109204368</v>
+        <v>149.6874174518</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -4815,19 +4809,19 @@
         <v>190</v>
       </c>
       <c r="B181" s="5">
-        <v>163610</v>
+        <v>747</v>
       </c>
       <c r="C181" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D181" s="5">
-        <v>12200431</v>
+        <v>104.597</v>
       </c>
       <c r="E181" s="6">
-        <v>-0.0252463025</v>
+        <v>0.99895403</v>
       </c>
       <c r="F181" s="7">
-        <v>72.7339404682</v>
+        <v>133.8688085676</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -4835,19 +4829,19 @@
         <v>191</v>
       </c>
       <c r="B182" s="5">
-        <v>783562</v>
+        <v>5128</v>
       </c>
       <c r="C182" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D182" s="5">
-        <v>87270501</v>
+        <v>1502932</v>
       </c>
       <c r="E182" s="6">
-        <v>-0.021902822</v>
+        <v>-0.0735228571</v>
       </c>
       <c r="F182" s="7">
-        <v>108.9894609488</v>
+        <v>273.0109204368</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -4855,19 +4849,19 @@
         <v>192</v>
       </c>
       <c r="B183" s="5">
-        <v>488100</v>
+        <v>163610</v>
       </c>
       <c r="C183" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D183" s="5">
-        <v>7364438</v>
+        <v>12200431</v>
       </c>
       <c r="E183" s="6">
-        <v>0.0180749333</v>
+        <v>-0.0252463025</v>
       </c>
       <c r="F183" s="7">
-        <v>15.3657037492</v>
+        <v>72.7339404682</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -4875,19 +4869,19 @@
         <v>193</v>
       </c>
       <c r="B184" s="5">
-        <v>26</v>
+        <v>783562</v>
       </c>
       <c r="C184" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D184" s="5">
-        <v>9.816</v>
+        <v>87270501</v>
       </c>
       <c r="E184" s="6">
-        <v>0.9990184</v>
+        <v>-0.021902822</v>
       </c>
       <c r="F184" s="7">
-        <v>384.6153846154</v>
+        <v>108.9894609488</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -4895,19 +4889,19 @@
         <v>194</v>
       </c>
       <c r="B185" s="5">
-        <v>241038</v>
+        <v>488100</v>
       </c>
       <c r="C185" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D185" s="5">
-        <v>48656601</v>
+        <v>7364438</v>
       </c>
       <c r="E185" s="6">
-        <v>0.02686798</v>
+        <v>0.0180749333</v>
       </c>
       <c r="F185" s="7">
-        <v>207.4361718899</v>
+        <v>15.3657037492</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -4915,19 +4909,19 @@
         <v>195</v>
       </c>
       <c r="B186" s="5">
-        <v>603550</v>
+        <v>26</v>
       </c>
       <c r="C186" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D186" s="5">
-        <v>37732836</v>
+        <v>9.816</v>
       </c>
       <c r="E186" s="6">
-        <v>0.0044106596</v>
+        <v>0.9990184</v>
       </c>
       <c r="F186" s="7">
-        <v>62.7951288211</v>
+        <v>384.6153846154</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -4935,19 +4929,19 @@
         <v>196</v>
       </c>
       <c r="B187" s="5">
-        <v>83600</v>
+        <v>241038</v>
       </c>
       <c r="C187" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D187" s="5">
-        <v>10642081</v>
+        <v>48656601</v>
       </c>
       <c r="E187" s="6">
-        <v>-0.0971217526</v>
+        <v>0.02686798</v>
       </c>
       <c r="F187" s="7">
-        <v>116.028708134</v>
+        <v>207.4361718899</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -4955,19 +4949,19 @@
         <v>197</v>
       </c>
       <c r="B188" s="5">
-        <v>243610</v>
+        <v>603550</v>
       </c>
       <c r="C188" t="s">
         <v>9</v>
       </c>
       <c r="D188" s="5">
-        <v>68682962</v>
+        <v>37732836</v>
       </c>
       <c r="E188" s="6">
-        <v>0.0074716474</v>
+        <v>0.0044106596</v>
       </c>
       <c r="F188" s="7">
-        <v>284.0605886458</v>
+        <v>62.7951288211</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -4975,19 +4969,19 @@
         <v>198</v>
       </c>
       <c r="B189" s="5">
-        <v>9826675</v>
+        <v>83600</v>
       </c>
       <c r="C189" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D189" s="5">
-        <v>343477335</v>
+        <v>10642081</v>
       </c>
       <c r="E189" s="6">
-        <v>-0.0204317736</v>
+        <v>-0.0971217526</v>
       </c>
       <c r="F189" s="7">
-        <v>34.253702295</v>
+        <v>116.028708134</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -4995,19 +4989,19 @@
         <v>199</v>
       </c>
       <c r="B190" s="5">
-        <v>176215</v>
+        <v>243610</v>
       </c>
       <c r="C190" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D190" s="5">
-        <v>3388081</v>
+        <v>68682962</v>
       </c>
       <c r="E190" s="6">
-        <v>0.0035055882</v>
+        <v>0.0074716474</v>
       </c>
       <c r="F190" s="7">
-        <v>19.2946116959</v>
+        <v>284.0605886458</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -5015,19 +5009,19 @@
         <v>200</v>
       </c>
       <c r="B191" s="5">
-        <v>447400</v>
+        <v>9826675</v>
       </c>
       <c r="C191" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D191" s="5">
-        <v>35652307</v>
+        <v>343477335</v>
       </c>
       <c r="E191" s="6">
-        <v>0.0416046505</v>
+        <v>-0.0204317736</v>
       </c>
       <c r="F191" s="7">
-        <v>83.1470719714</v>
+        <v>34.253702295</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -5035,19 +5029,19 @@
         <v>201</v>
       </c>
       <c r="B192" s="5">
-        <v>12189</v>
+        <v>176215</v>
       </c>
       <c r="C192" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D192" s="5">
-        <v>320.409</v>
+        <v>3388081</v>
       </c>
       <c r="E192" s="6">
-        <v>0.99893197</v>
+        <v>0.0035055882</v>
       </c>
       <c r="F192" s="7">
-        <v>24.6123554024</v>
+        <v>19.2946116959</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -5055,19 +5049,19 @@
         <v>202</v>
       </c>
       <c r="B193" s="5">
-        <v>44</v>
+        <v>447400</v>
       </c>
       <c r="C193" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D193" s="5">
-        <v>496</v>
+        <v>35652307</v>
       </c>
       <c r="E193" s="6">
-        <v>0.4376417234</v>
+        <v>0.0416046505</v>
       </c>
       <c r="F193" s="7">
-        <v>20.0454545455</v>
+        <v>83.1470719714</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -5075,19 +5069,19 @@
         <v>203</v>
       </c>
       <c r="B194" s="5">
-        <v>912050</v>
+        <v>12189</v>
       </c>
       <c r="C194" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D194" s="5">
-        <v>28300854</v>
+        <v>320.409</v>
       </c>
       <c r="E194" s="6">
-        <v>0.0034910563</v>
+        <v>0.99893197</v>
       </c>
       <c r="F194" s="7">
-        <v>31.1386437147</v>
+        <v>24.6123554024</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -5095,19 +5089,19 @@
         <v>204</v>
       </c>
       <c r="B195" s="5">
-        <v>331210</v>
+        <v>44</v>
       </c>
       <c r="C195" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D195" s="5">
-        <v>100352192</v>
+        <v>496</v>
       </c>
       <c r="E195" s="6">
-        <v>0.0073967161</v>
+        <v>0.4376417234</v>
       </c>
       <c r="F195" s="7">
-        <v>305.2444068718</v>
+        <v>20.0454545455</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -5115,19 +5109,19 @@
         <v>205</v>
       </c>
       <c r="B196" s="5">
-        <v>527968</v>
+        <v>912050</v>
       </c>
       <c r="C196" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D196" s="5">
-        <v>39390799</v>
+        <v>28300854</v>
       </c>
       <c r="E196" s="6">
-        <v>0.0297832759</v>
+        <v>0.0034910563</v>
       </c>
       <c r="F196" s="7">
-        <v>76.8985999151</v>
+        <v>31.1386437147</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -5135,19 +5129,19 @@
         <v>206</v>
       </c>
       <c r="B197" s="5">
-        <v>752618</v>
+        <v>331210</v>
       </c>
       <c r="C197" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D197" s="5">
-        <v>20723965</v>
+        <v>100352192</v>
       </c>
       <c r="E197" s="6">
-        <v>0.0270438967</v>
+        <v>0.0073967161</v>
       </c>
       <c r="F197" s="7">
-        <v>28.3012099099</v>
+        <v>305.2444068718</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -5155,19 +5149,19 @@
         <v>207</v>
       </c>
       <c r="B198" s="5">
-        <v>390757</v>
+        <v>527968</v>
       </c>
       <c r="C198" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D198" s="5">
-        <v>16340822</v>
+        <v>39390799</v>
       </c>
       <c r="E198" s="6">
-        <v>0.0156131325</v>
+        <v>0.0297832759</v>
       </c>
       <c r="F198" s="7">
-        <v>42.4816446027</v>
+        <v>76.8985999151</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -5175,19 +5169,19 @@
         <v>208</v>
       </c>
       <c r="B199" s="5">
-        <v>31903172</v>
+        <v>752618</v>
       </c>
       <c r="C199" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D199" s="5">
-        <v>4767308287.3280000687</v>
+        <v>20723965</v>
       </c>
       <c r="E199" s="6">
-        <v>-110.9086452424</v>
+        <v>0.0270438967</v>
       </c>
       <c r="F199" s="7">
-        <v>1.3352904219</v>
+        <v>28.3012099099</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -5195,19 +5189,19 @@
         <v>209</v>
       </c>
       <c r="B200" s="5">
-        <v>30046306</v>
+        <v>390757</v>
       </c>
       <c r="C200" t="s">
         <v>11</v>
       </c>
       <c r="D200" s="5">
-        <v>1477264796.5399999619</v>
+        <v>16340822</v>
       </c>
       <c r="E200" s="6">
-        <v>-12.897128848</v>
+        <v>0.0156131325</v>
       </c>
       <c r="F200" s="7">
-        <v>3.5378725092</v>
+        <v>42.4816446027</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -5215,19 +5209,19 @@
         <v>210</v>
       </c>
       <c r="B201" s="5">
-        <v>22998356</v>
+        <v>31903172</v>
       </c>
       <c r="C201" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D201" s="5">
-        <v>742847938.3069999218</v>
+        <v>4767308287.3280000687</v>
       </c>
       <c r="E201" s="6">
-        <v>-264.3028351096</v>
+        <v>-110.9086452424</v>
       </c>
       <c r="F201" s="7">
-        <v>0.1217478328</v>
+        <v>1.3352904219</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -5235,19 +5229,19 @@
         <v>211</v>
       </c>
       <c r="B202" s="5">
-        <v>40249922</v>
+        <v>30046306</v>
       </c>
       <c r="C202" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D202" s="5">
-        <v>1033579930.3939999342</v>
+        <v>1477264796.5399999619</v>
       </c>
       <c r="E202" s="6">
-        <v>-10334.79930394</v>
+        <v>-12.897128848</v>
       </c>
       <c r="F202" s="7">
-        <v>0.0024844769</v>
+        <v>3.5378725092</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -5255,19 +5249,59 @@
         <v>212</v>
       </c>
       <c r="B203" s="5">
-        <v>8536907</v>
+        <v>22998356</v>
       </c>
       <c r="C203" t="s">
+        <v>9</v>
+      </c>
+      <c r="D203" s="5">
+        <v>742847938.3069999218</v>
+      </c>
+      <c r="E203" s="6">
+        <v>-264.3028351096</v>
+      </c>
+      <c r="F203" s="7">
+        <v>0.1217478328</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>213</v>
+      </c>
+      <c r="B204" s="5">
+        <v>40249922</v>
+      </c>
+      <c r="C204" t="s">
+        <v>15</v>
+      </c>
+      <c r="D204" s="5">
+        <v>1033579930.3939999342</v>
+      </c>
+      <c r="E204" s="6">
+        <v>-10334.79930394</v>
+      </c>
+      <c r="F204" s="7">
+        <v>0.0024844769</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>214</v>
+      </c>
+      <c r="B205" s="5">
+        <v>8536680</v>
+      </c>
+      <c r="C205" t="s">
         <v>19</v>
       </c>
-      <c r="D203" s="5">
-        <v>42016284.2240000069</v>
-      </c>
-      <c r="E203" s="6">
-        <v>-0.5390580302</v>
-      </c>
-      <c r="F203" s="7">
-        <v>3.197879513</v>
+      <c r="D205" s="5">
+        <v>42016300.2630000189</v>
+      </c>
+      <c r="E205" s="6">
+        <v>-0.5390586177</v>
+      </c>
+      <c r="F205" s="7">
+        <v>3.1979645483</v>
       </c>
     </row>
   </sheetData>
@@ -5302,65 +5336,65 @@
     <!-- $Insert Data$ -->
     <row r="1" spans="1:12" x14ac:dyDescent="0.25" customHeight="1" ht="30">
       <c r="A1" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B2" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="10">
         <v>1</v>
       </c>
       <c r="D2" s="11">
-        <v>8</v>
-      </c>
-      <c r="E2" s="9">
+        <v>9</v>
+      </c>
+      <c r="E2" s="12">
         <v>3</v>
       </c>
-      <c r="F2" s="12">
-        <v>7</v>
-      </c>
-      <c r="G2" s="13">
-        <v>12</v>
-      </c>
-      <c r="H2" s="14">
+      <c r="F2" s="13">
+        <v>6</v>
+      </c>
+      <c r="G2" s="14">
+        <v>11</v>
+      </c>
+      <c r="H2" s="15">
         <v>2</v>
       </c>
       <c r="I2" s="10">
@@ -5369,30 +5403,30 @@
       <c r="J2" s="10">
         <v>1</v>
       </c>
-      <c r="K2" s="15">
-        <v>0</v>
-      </c>
-      <c r="L2" s="15">
+      <c r="K2" s="16">
+        <v>0</v>
+      </c>
+      <c r="L2" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="B3" s="15">
-        <v>0</v>
-      </c>
-      <c r="C3" s="15">
-        <v>0</v>
-      </c>
-      <c r="D3" s="9">
+        <v>227</v>
+      </c>
+      <c r="B3" s="16">
+        <v>0</v>
+      </c>
+      <c r="C3" s="16">
+        <v>0</v>
+      </c>
+      <c r="D3" s="12">
         <v>3</v>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="9">
         <v>4</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="15">
         <v>2</v>
       </c>
       <c r="G3" s="10">
@@ -5401,217 +5435,217 @@
       <c r="H3" s="10">
         <v>1</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="16">
         <v>0</v>
       </c>
       <c r="J3" s="10">
         <v>1</v>
       </c>
-      <c r="K3" s="15">
-        <v>0</v>
-      </c>
-      <c r="L3" s="15">
+      <c r="K3" s="16">
+        <v>0</v>
+      </c>
+      <c r="L3" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="B4" s="16">
+        <v>228</v>
+      </c>
+      <c r="B4" s="9">
         <v>4</v>
       </c>
       <c r="C4" s="10">
         <v>1</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="15">
         <v>2</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="17">
         <v>7</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="12">
         <v>3</v>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="9">
         <v>4</v>
       </c>
-      <c r="H4" s="15">
-        <v>0</v>
-      </c>
-      <c r="I4" s="15">
-        <v>0</v>
-      </c>
-      <c r="J4" s="15">
-        <v>0</v>
-      </c>
-      <c r="K4" s="15">
-        <v>0</v>
-      </c>
-      <c r="L4" s="15">
+      <c r="H4" s="16">
+        <v>0</v>
+      </c>
+      <c r="I4" s="16">
+        <v>0</v>
+      </c>
+      <c r="J4" s="16">
+        <v>0</v>
+      </c>
+      <c r="K4" s="16">
+        <v>0</v>
+      </c>
+      <c r="L4" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="B5" s="14">
+        <v>229</v>
+      </c>
+      <c r="B5" s="15">
         <v>2</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="17">
         <v>7</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="18">
         <v>5</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="9">
         <v>4</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="17">
         <v>7</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="12">
         <v>3</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="15">
         <v>2</v>
       </c>
-      <c r="I5" s="15">
-        <v>0</v>
-      </c>
-      <c r="J5" s="15">
+      <c r="I5" s="16">
+        <v>0</v>
+      </c>
+      <c r="J5" s="16">
         <v>0</v>
       </c>
       <c r="K5" s="10">
         <v>1</v>
       </c>
-      <c r="L5" s="15">
+      <c r="L5" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="B6" s="15">
-        <v>0</v>
-      </c>
-      <c r="C6" s="9">
+        <v>230</v>
+      </c>
+      <c r="B6" s="16">
+        <v>0</v>
+      </c>
+      <c r="C6" s="12">
         <v>3</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="18">
         <v>5</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="19">
         <v>10</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="17">
         <v>7</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="9">
         <v>4</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="15">
         <v>2</v>
       </c>
-      <c r="I6" s="15">
-        <v>0</v>
-      </c>
-      <c r="J6" s="15">
-        <v>0</v>
-      </c>
-      <c r="K6" s="15">
-        <v>0</v>
-      </c>
-      <c r="L6" s="15">
+      <c r="I6" s="16">
+        <v>0</v>
+      </c>
+      <c r="J6" s="16">
+        <v>0</v>
+      </c>
+      <c r="K6" s="16">
+        <v>0</v>
+      </c>
+      <c r="L6" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="B7" s="9">
+        <v>231</v>
+      </c>
+      <c r="B7" s="12">
         <v>3</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="9">
         <v>4</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="13">
         <v>6</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="19">
         <v>10</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="13">
         <v>6</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="9">
         <v>4</v>
       </c>
       <c r="H7" s="10">
         <v>1</v>
       </c>
-      <c r="I7" s="15">
-        <v>0</v>
-      </c>
-      <c r="J7" s="15">
-        <v>0</v>
-      </c>
-      <c r="K7" s="15">
-        <v>0</v>
-      </c>
-      <c r="L7" s="15">
+      <c r="I7" s="16">
+        <v>0</v>
+      </c>
+      <c r="J7" s="16">
+        <v>0</v>
+      </c>
+      <c r="K7" s="16">
+        <v>0</v>
+      </c>
+      <c r="L7" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="B8" s="15">
-        <v>0</v>
-      </c>
-      <c r="C8" s="15">
-        <v>0</v>
-      </c>
-      <c r="D8" s="14">
+        <v>232</v>
+      </c>
+      <c r="B8" s="16">
+        <v>0</v>
+      </c>
+      <c r="C8" s="16">
+        <v>0</v>
+      </c>
+      <c r="D8" s="15">
         <v>2</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="18">
         <v>5</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="9">
         <v>4</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="15">
         <v>2</v>
       </c>
       <c r="H8" s="10">
         <v>1</v>
       </c>
-      <c r="I8" s="15">
-        <v>0</v>
-      </c>
-      <c r="J8" s="15">
-        <v>0</v>
-      </c>
-      <c r="K8" s="15">
-        <v>0</v>
-      </c>
-      <c r="L8" s="15">
+      <c r="I8" s="16">
+        <v>0</v>
+      </c>
+      <c r="J8" s="16">
+        <v>0</v>
+      </c>
+      <c r="K8" s="16">
+        <v>0</v>
+      </c>
+      <c r="L8" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B9" s="10">
         <v>1</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="16">
         <v>0</v>
       </c>
       <c r="D9" s="10">
@@ -5620,118 +5654,118 @@
       <c r="E9" s="10">
         <v>1</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="15">
         <v>2</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="12">
         <v>3</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="16">
         <v>0</v>
       </c>
       <c r="I9" s="10">
         <v>1</v>
       </c>
-      <c r="J9" s="15">
-        <v>0</v>
-      </c>
-      <c r="K9" s="15">
-        <v>0</v>
-      </c>
-      <c r="L9" s="15">
+      <c r="J9" s="16">
+        <v>0</v>
+      </c>
+      <c r="K9" s="16">
+        <v>0</v>
+      </c>
+      <c r="L9" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="B10" s="15">
-        <v>0</v>
-      </c>
-      <c r="C10" s="15">
-        <v>0</v>
-      </c>
-      <c r="D10" s="14">
+        <v>234</v>
+      </c>
+      <c r="B10" s="16">
+        <v>0</v>
+      </c>
+      <c r="C10" s="16">
+        <v>0</v>
+      </c>
+      <c r="D10" s="15">
         <v>2</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="16">
         <v>0</v>
       </c>
       <c r="F10" s="10">
         <v>1</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="15">
         <v>2</v>
       </c>
-      <c r="H10" s="15">
-        <v>0</v>
-      </c>
-      <c r="I10" s="15">
-        <v>0</v>
-      </c>
-      <c r="J10" s="15">
-        <v>0</v>
-      </c>
-      <c r="K10" s="15">
-        <v>0</v>
-      </c>
-      <c r="L10" s="15">
+      <c r="H10" s="16">
+        <v>0</v>
+      </c>
+      <c r="I10" s="16">
+        <v>0</v>
+      </c>
+      <c r="J10" s="16">
+        <v>0</v>
+      </c>
+      <c r="K10" s="16">
+        <v>0</v>
+      </c>
+      <c r="L10" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="B11" s="15">
-        <v>0</v>
-      </c>
-      <c r="C11" s="15">
-        <v>0</v>
-      </c>
-      <c r="D11" s="15">
-        <v>0</v>
-      </c>
-      <c r="E11" s="15">
-        <v>0</v>
-      </c>
-      <c r="F11" s="15">
-        <v>0</v>
-      </c>
-      <c r="G11" s="15">
-        <v>0</v>
-      </c>
-      <c r="H11" s="15">
-        <v>0</v>
-      </c>
-      <c r="I11" s="15">
-        <v>0</v>
-      </c>
-      <c r="J11" s="15">
-        <v>0</v>
-      </c>
-      <c r="K11" s="15">
-        <v>0</v>
-      </c>
-      <c r="L11" s="15">
+        <v>235</v>
+      </c>
+      <c r="B11" s="16">
+        <v>0</v>
+      </c>
+      <c r="C11" s="16">
+        <v>0</v>
+      </c>
+      <c r="D11" s="16">
+        <v>0</v>
+      </c>
+      <c r="E11" s="16">
+        <v>0</v>
+      </c>
+      <c r="F11" s="16">
+        <v>0</v>
+      </c>
+      <c r="G11" s="16">
+        <v>0</v>
+      </c>
+      <c r="H11" s="16">
+        <v>0</v>
+      </c>
+      <c r="I11" s="16">
+        <v>0</v>
+      </c>
+      <c r="J11" s="16">
+        <v>0</v>
+      </c>
+      <c r="K11" s="16">
+        <v>0</v>
+      </c>
+      <c r="L11" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="B12" s="15">
-        <v>0</v>
-      </c>
-      <c r="C12" s="15">
-        <v>0</v>
-      </c>
-      <c r="D12" s="15">
-        <v>0</v>
-      </c>
-      <c r="E12" s="15">
+        <v>236</v>
+      </c>
+      <c r="B12" s="16">
+        <v>0</v>
+      </c>
+      <c r="C12" s="16">
+        <v>0</v>
+      </c>
+      <c r="D12" s="16">
+        <v>0</v>
+      </c>
+      <c r="E12" s="16">
         <v>0</v>
       </c>
       <c r="F12" s="10">
@@ -5740,19 +5774,19 @@
       <c r="G12" s="10">
         <v>1</v>
       </c>
-      <c r="H12" s="15">
-        <v>0</v>
-      </c>
-      <c r="I12" s="15">
-        <v>0</v>
-      </c>
-      <c r="J12" s="15">
-        <v>0</v>
-      </c>
-      <c r="K12" s="15">
-        <v>0</v>
-      </c>
-      <c r="L12" s="15">
+      <c r="H12" s="16">
+        <v>0</v>
+      </c>
+      <c r="I12" s="16">
+        <v>0</v>
+      </c>
+      <c r="J12" s="16">
+        <v>0</v>
+      </c>
+      <c r="K12" s="16">
+        <v>0</v>
+      </c>
+      <c r="L12" s="16">
         <v>0</v>
       </c>
     </row>
